--- a/tests/SafeOpenXml.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9e6b8518c5ad40e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5eee87d7d6634d97"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rae2d77b917f24e77"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R5e70d5d3bf894244"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5eee87d7d6634d97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R32928c14e5c64aae"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R5e70d5d3bf894244"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R73b1086b68714e76"/>
   </x:pivotCaches>
 </x:workbook>
 </file>
